--- a/manual_testing/SauceDemo_test_run.xlsx
+++ b/manual_testing/SauceDemo_test_run.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sandra\Documents\IT Bootcamp\Projekat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417E894A-3EF2-4A5F-8A8C-DA9EE78D2065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85327027-9FBF-4D13-A8D0-BBBB1B42FEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1860" windowWidth="26295" windowHeight="15420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21540" windowHeight="15420" tabRatio="500" firstSheet="15" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TC_1_1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="178">
   <si>
     <t>ID</t>
   </si>
@@ -319,9 +319,6 @@
   </si>
   <si>
     <t>"1234" is in First name text field</t>
-  </si>
-  <si>
-    <t>User is logged in as standard_user and is on Checkout-step-one page</t>
   </si>
   <si>
     <t>TC_6_3</t>
@@ -547,9 +544,6 @@
     <t>Blocked</t>
   </si>
   <si>
-    <t>Continue button can be clicked and User is on Checkout-step-one page. Error message is not shown</t>
-  </si>
-  <si>
     <t>User is on Checkout-step-two page with total price of $0.00</t>
   </si>
   <si>
@@ -653,6 +647,15 @@
   </si>
   <si>
     <t>Cursor is in Quantity field and user can input a number 3</t>
+  </si>
+  <si>
+    <t>Checkout button cannot be clicked. Error message is shown indicating that a Cart can not be empty</t>
+  </si>
+  <si>
+    <t>Checkout button can be clicked and User is on Checkout-step-one page. Error message is not shown</t>
+  </si>
+  <si>
+    <t>User is logged in as standard_user and on Cart page containing one item</t>
   </si>
 </sst>
 </file>
@@ -1962,34 +1965,34 @@
         <v>1</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="22"/>
     </row>
     <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="24"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="30" x14ac:dyDescent="0.25">
@@ -1997,7 +2000,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>4</v>
@@ -2011,7 +2014,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>5</v>
@@ -2119,7 +2122,7 @@
     <row r="21" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="18"/>
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="17"/>
@@ -2127,20 +2130,20 @@
     <row r="22" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="18"/>
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E22" s="17"/>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="18"/>
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
       <c r="E23" s="17"/>
     </row>
@@ -2152,34 +2155,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
@@ -2223,34 +2226,34 @@
         <v>37</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>38</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -2261,10 +2264,10 @@
         <v>39</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="30" x14ac:dyDescent="0.25">
@@ -2366,24 +2369,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2392,34 +2395,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2460,34 +2463,34 @@
         <v>41</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>42</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -2498,10 +2501,10 @@
         <v>30</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -2512,10 +2515,10 @@
         <v>31</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
@@ -2611,24 +2614,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2637,34 +2640,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2705,34 +2708,34 @@
         <v>43</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -2848,24 +2851,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2874,34 +2877,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2942,36 +2945,36 @@
         <v>49</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E3" s="49" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -2979,13 +2982,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
@@ -3079,24 +3082,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3105,34 +3108,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3173,34 +3176,34 @@
         <v>51</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D3" s="48" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="30" x14ac:dyDescent="0.25">
@@ -3208,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
@@ -3308,24 +3311,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3334,34 +3337,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3402,34 +3405,34 @@
         <v>52</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -3553,24 +3556,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3579,34 +3582,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3647,36 +3650,36 @@
         <v>61</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="49" t="s">
         <v>144</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" s="49" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -3684,13 +3687,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="30" x14ac:dyDescent="0.25">
@@ -3698,7 +3701,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>66</v>
@@ -3712,7 +3715,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>67</v>
@@ -3726,7 +3729,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>68</v>
@@ -3743,10 +3746,10 @@
         <v>62</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3757,10 +3760,10 @@
         <v>70</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
@@ -3804,7 +3807,7 @@
     <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="19"/>
       <c r="C17" s="36" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -3824,24 +3827,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3850,34 +3853,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3918,34 +3921,34 @@
         <v>63</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -3967,7 +3970,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>66</v>
@@ -3981,7 +3984,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>67</v>
@@ -3995,7 +3998,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>68</v>
@@ -4093,24 +4096,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4119,34 +4122,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -4187,34 +4190,34 @@
         <v>73</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -4236,7 +4239,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>66</v>
@@ -4250,7 +4253,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>75</v>
@@ -4378,24 +4381,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4404,34 +4407,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -4472,36 +4475,36 @@
         <v>84</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E3" s="49" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -4523,7 +4526,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>85</v>
@@ -4537,7 +4540,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>67</v>
@@ -4551,7 +4554,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>68</v>
@@ -4568,10 +4571,10 @@
         <v>62</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -4582,10 +4585,10 @@
         <v>70</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
@@ -4629,7 +4632,7 @@
     <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="19"/>
       <c r="C17" s="36" t="s">
-        <v>86</v>
+        <v>177</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -4649,24 +4652,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4675,34 +4678,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -4743,34 +4746,34 @@
         <v>10</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4778,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -4792,7 +4795,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>5</v>
@@ -4809,10 +4812,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -4894,24 +4897,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4920,34 +4923,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -4985,39 +4988,39 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E3" s="49" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -5039,7 +5042,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>66</v>
@@ -5053,13 +5056,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="30" x14ac:dyDescent="0.25">
@@ -5067,7 +5070,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>68</v>
@@ -5084,10 +5087,10 @@
         <v>62</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -5098,10 +5101,10 @@
         <v>70</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
@@ -5145,7 +5148,7 @@
     <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="19"/>
       <c r="C17" s="36" t="s">
-        <v>86</v>
+        <v>177</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -5165,24 +5168,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5191,34 +5194,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -5256,37 +5259,37 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -5308,13 +5311,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="E6" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="30" x14ac:dyDescent="0.25">
@@ -5322,7 +5325,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>67</v>
@@ -5336,7 +5339,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>68</v>
@@ -5353,10 +5356,10 @@
         <v>62</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
@@ -5406,7 +5409,7 @@
     <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="19"/>
       <c r="C17" s="36" t="s">
-        <v>86</v>
+        <v>177</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -5426,24 +5429,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5452,34 +5455,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -5517,37 +5520,37 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -5569,7 +5572,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>66</v>
@@ -5583,7 +5586,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>75</v>
@@ -5597,7 +5600,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>68</v>
@@ -5614,10 +5617,10 @@
         <v>62</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
@@ -5667,7 +5670,7 @@
     <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="19"/>
       <c r="C17" s="36" t="s">
-        <v>86</v>
+        <v>177</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -5687,24 +5690,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5713,34 +5716,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -5778,37 +5781,37 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -5830,7 +5833,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>66</v>
@@ -5844,7 +5847,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>75</v>
@@ -5875,10 +5878,10 @@
         <v>62</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
@@ -5928,7 +5931,7 @@
     <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="19"/>
       <c r="C17" s="36" t="s">
-        <v>86</v>
+        <v>177</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -5948,24 +5951,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5974,34 +5977,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -6042,34 +6045,34 @@
         <v>12</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="30" x14ac:dyDescent="0.25">
@@ -6077,7 +6080,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>4</v>
@@ -6091,7 +6094,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>13</v>
@@ -6108,10 +6111,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -6193,24 +6196,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6219,34 +6222,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -6287,34 +6290,34 @@
         <v>14</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -6336,7 +6339,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>5</v>
@@ -6353,10 +6356,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -6438,24 +6441,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6464,34 +6467,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -6532,34 +6535,34 @@
         <v>17</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="30" x14ac:dyDescent="0.25">
@@ -6567,7 +6570,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
@@ -6598,10 +6601,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -6683,24 +6686,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6709,34 +6712,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -6777,34 +6780,34 @@
         <v>21</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -6843,10 +6846,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -6928,24 +6931,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6954,34 +6957,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -7022,34 +7025,34 @@
         <v>22</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -7060,10 +7063,10 @@
         <v>24</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="30" x14ac:dyDescent="0.25">
@@ -7165,24 +7168,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7191,34 +7194,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -7259,34 +7262,34 @@
         <v>28</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -7297,10 +7300,10 @@
         <v>30</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -7311,10 +7314,10 @@
         <v>31</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
@@ -7409,24 +7412,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7435,34 +7438,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -7503,34 +7506,34 @@
         <v>33</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -7541,10 +7544,10 @@
         <v>24</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -7555,10 +7558,10 @@
         <v>34</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -7569,10 +7572,10 @@
         <v>35</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="30" x14ac:dyDescent="0.25">
@@ -7661,24 +7664,24 @@
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="39" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7687,34 +7690,34 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C28" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
